--- a/gte/nodes/HPT/turbine_cooling.xlsx
+++ b/gte/nodes/HPT/turbine_cooling.xlsx
@@ -1603,112 +1603,112 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>86.525815603707784</v>
+        <v>86.350031862380533</v>
       </c>
       <c r="C3">
-        <v>87.054099747580949</v>
+        <v>86.866588025249484</v>
       </c>
       <c r="D3">
-        <v>85.723219878099087</v>
+        <v>85.535901263577458</v>
       </c>
       <c r="E3">
-        <v>87.030656130375917</v>
+        <v>86.834755019794926</v>
       </c>
       <c r="F3">
-        <v>83.714653398232954</v>
+        <v>83.528028143862244</v>
       </c>
       <c r="G3">
-        <v>448.33713104322396</v>
+        <v>448.32662689953912</v>
       </c>
       <c r="H3">
         <v>14893</v>
       </c>
       <c r="I3">
-        <v>459.094088117501</v>
+        <v>459.10364394409055</v>
       </c>
       <c r="J3">
-        <v>1.6566004287246656</v>
+        <v>1.656634910080089</v>
       </c>
       <c r="K3">
-        <v>535.55394765892618</v>
+        <v>536.73795115500127</v>
       </c>
       <c r="L3">
         <v>0.16</v>
       </c>
       <c r="M3">
-        <v>449.86531603349795</v>
+        <v>450.85987897020107</v>
       </c>
       <c r="N3">
         <v>1.2827688517497748</v>
       </c>
       <c r="O3">
-        <v>1.2927802022669293</v>
+        <v>1.2928060950349531</v>
       </c>
       <c r="P3">
-        <v>1.2954705533570881</v>
+        <v>1.2954725538245488</v>
       </c>
       <c r="Q3">
         <v>2731.8</v>
       </c>
       <c r="R3">
-        <v>2414.4666913734436</v>
+        <v>2413.7074417616545</v>
       </c>
       <c r="S3">
-        <v>872.8720844382259</v>
+        <v>870.4517592730466</v>
       </c>
       <c r="T3">
         <v>2705.1983504889472</v>
       </c>
       <c r="U3">
-        <v>1019.733454965007</v>
+        <v>1017.2538035617159</v>
       </c>
       <c r="V3">
-        <v>840.66818361621063</v>
+        <v>838.14532757351526</v>
       </c>
       <c r="W3">
         <v>1773</v>
       </c>
       <c r="X3">
-        <v>1758.9562299548395</v>
+        <v>1758.9932072717177</v>
       </c>
       <c r="Y3">
-        <v>1394.1636317648961</v>
+        <v>1394.1838085136349</v>
       </c>
       <c r="Z3">
         <v>1769.1806090782168</v>
       </c>
       <c r="AA3">
-        <v>1447.6373514402683</v>
+        <v>1446.9556017980667</v>
       </c>
       <c r="AB3">
-        <v>1382.2678993449</v>
+        <v>1382.2157190991907</v>
       </c>
       <c r="AC3">
         <v>0.1886773190833678</v>
       </c>
       <c r="AD3">
-        <v>0.40955706628258232</v>
+        <v>0.41036205321936892</v>
       </c>
       <c r="AE3">
-        <v>0.48562657782485164</v>
+        <v>0.48707889263145809</v>
       </c>
       <c r="AF3">
         <v>5.34064271677014</v>
       </c>
       <c r="AG3">
-        <v>4.7580047901266287</v>
+        <v>4.7564086043237728</v>
       </c>
       <c r="AH3">
-        <v>2.1701879135223678</v>
+        <v>2.1641390095626272</v>
       </c>
       <c r="AI3">
         <v>5.300054107500574</v>
       </c>
       <c r="AJ3">
-        <v>2.4416621817239736</v>
+        <v>2.4368724938254123</v>
       </c>
       <c r="AK3">
-        <v>2.0591953687523765</v>
+        <v>2.0530555011272824</v>
       </c>
       <c r="AL3">
         <v>32.193039999999996</v>
@@ -1717,7 +1717,7 @@
         <v>33.049726105303172</v>
       </c>
       <c r="AN3">
-        <v>33.350889868874951</v>
+        <v>33.35009352222292</v>
       </c>
       <c r="AO3">
         <v>2.267</v>
@@ -1726,154 +1726,154 @@
         <v>2.2936109104732938</v>
       </c>
       <c r="AQ3">
-        <v>2.3027233540261451</v>
+        <v>2.3026992586176238</v>
       </c>
       <c r="AR3">
         <v>0.431918799265738</v>
       </c>
       <c r="AS3">
-        <v>0.20657308502835017</v>
+        <v>0.20613945695080096</v>
       </c>
       <c r="AT3">
         <v>0.026610910473294051</v>
       </c>
       <c r="AU3">
-        <v>0.0091124435528514881</v>
+        <v>0.0090883481443300509</v>
       </c>
       <c r="AV3">
         <v>809.15851417200838</v>
       </c>
       <c r="AW3">
-        <v>734.78941572209158</v>
+        <v>734.62373134468726</v>
       </c>
       <c r="AX3">
-        <v>718.752951871204</v>
+        <v>718.73994423109059</v>
       </c>
       <c r="AY3">
         <v>758.20373510241677</v>
       </c>
       <c r="AZ3">
-        <v>756.47451997194889</v>
+        <v>756.48577545889464</v>
       </c>
       <c r="BA3">
-        <v>673.78220950868274</v>
+        <v>673.7873153829978</v>
       </c>
       <c r="BB3">
         <v>0</v>
       </c>
       <c r="BC3">
-        <v>700.89245579044</v>
+        <v>700.81145219987718</v>
       </c>
       <c r="BD3">
-        <v>698.96961601073667</v>
+        <v>698.88630114509442</v>
       </c>
       <c r="BE3">
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>891.54925936768836</v>
+        <v>892.54820797189382</v>
       </c>
       <c r="BG3">
-        <v>173.52400506279335</v>
+        <v>174.05036593062957</v>
       </c>
       <c r="BH3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="BI3">
-        <v>863.25008660391779</v>
+        <v>864.16869317101214</v>
       </c>
       <c r="BJ3">
-        <v>-1.7310505108591769</v>
+        <v>-2.6540040514472594</v>
       </c>
       <c r="BK3">
         <v>100</v>
       </c>
       <c r="BL3">
-        <v>222.84382391576858</v>
+        <v>223.28182482446738</v>
       </c>
       <c r="BM3">
-        <v>173.51537049253355</v>
+        <v>174.03012998639335</v>
       </c>
       <c r="BN3">
         <v>0</v>
       </c>
       <c r="BO3">
-        <v>398.51579779794986</v>
+        <v>399.52231406257067</v>
       </c>
       <c r="BP3">
-        <v>546.54394864616222</v>
+        <v>545.83272681938092</v>
       </c>
       <c r="BQ3">
         <v>0</v>
       </c>
       <c r="BR3">
-        <v>330.3868508841332</v>
+        <v>331.30545745122771</v>
       </c>
       <c r="BS3">
-        <v>518.26894948914082</v>
+        <v>517.34599594855274</v>
       </c>
       <c r="BT3">
         <v>0</v>
       </c>
       <c r="BU3">
-        <v>222.84382391576841</v>
+        <v>223.28182482446735</v>
       </c>
       <c r="BV3">
-        <v>173.51537049253355</v>
+        <v>174.03012998639335</v>
       </c>
       <c r="BW3">
         <v>0.13189067182119879</v>
       </c>
       <c r="BX3">
-        <v>1.1785582142287465</v>
+        <v>1.1798611909529453</v>
       </c>
       <c r="BY3">
-        <v>0.25753723178492027</v>
+        <v>0.25831647755448606</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>0.56858337467553255</v>
+        <v>0.57008531011936658</v>
       </c>
       <c r="CB3">
-        <v>0.78192804969904006</v>
+        <v>0.78100361378532968</v>
       </c>
       <c r="CC3">
         <v>0.12358517923070672</v>
       </c>
       <c r="CD3">
-        <v>1.2133398226640839</v>
+        <v>1.2149732848108987</v>
       </c>
       <c r="CE3">
-        <v>0.24142371118065026</v>
+        <v>0.24216041883803882</v>
       </c>
       <c r="CF3">
         <v>0</v>
       </c>
       <c r="CG3">
-        <v>0.54235375370278138</v>
+        <v>0.54384618549045183</v>
       </c>
       <c r="CH3">
-        <v>0.7604058490796981</v>
+        <v>0.759430070918507</v>
       </c>
       <c r="CI3">
         <v>90</v>
       </c>
       <c r="CJ3">
-        <v>14.474625580113765</v>
+        <v>14.487110650698016</v>
       </c>
       <c r="CK3">
-        <v>90.571583934412843</v>
+        <v>90.87370758242173</v>
       </c>
       <c r="CL3">
         <v>0</v>
       </c>
       <c r="CM3">
-        <v>33.999413467386489</v>
+        <v>33.977823162023896</v>
       </c>
       <c r="CN3">
-        <v>18.510439199819007</v>
+        <v>18.592435694827742</v>
       </c>
       <c r="CO3">
         <v>36</v>
@@ -1882,16 +1882,16 @@
         <v>89</v>
       </c>
       <c r="CQ3">
-        <v>37.02154050549202</v>
+        <v>37.030857575330955</v>
       </c>
       <c r="CR3">
-        <v>67.049276140187331</v>
+        <v>67.075544186851488</v>
       </c>
       <c r="CS3">
-        <v>0.87192947090361528</v>
+        <v>0.87173231584331334</v>
       </c>
       <c r="CT3">
-        <v>0.72529914769855308</v>
+        <v>0.72424837282524945</v>
       </c>
       <c r="CU3">
         <v>59.207026191087152</v>
@@ -1900,79 +1900,79 @@
         <v>23.659847993703021</v>
       </c>
       <c r="CW3">
-        <v>67.985749212265219</v>
+        <v>67.971093724932061</v>
       </c>
       <c r="CX3">
-        <v>32.681828304144716</v>
+        <v>32.675488079460088</v>
       </c>
       <c r="CY3">
-        <v>0.9459272602787695</v>
+        <v>0.94580823651969093</v>
       </c>
       <c r="CZ3">
-        <v>0.968521747425131</v>
+        <v>0.96567163292182356</v>
       </c>
       <c r="DA3">
-        <v>0.013980745656407868</v>
+        <v>0.013980417290494221</v>
       </c>
       <c r="DB3">
-        <v>0.026224102241371214</v>
+        <v>0.026197244239498662</v>
       </c>
       <c r="DC3">
-        <v>0.027563897830483578</v>
+        <v>0.027534714002366085</v>
       </c>
       <c r="DD3">
-        <v>0.011312403309499104</v>
+        <v>0.016893120002848219</v>
       </c>
       <c r="DE3">
-        <v>-0.0013471110768567892</v>
+        <v>-0.0013465483731770187</v>
       </c>
       <c r="DF3">
-        <v>0.00083810061608503459</v>
+        <v>0.00085122482289059229</v>
       </c>
       <c r="DG3">
-        <v>0.024096132990375791</v>
+        <v>0.024343900966191996</v>
       </c>
       <c r="DH3">
-        <v>0.00023100243169450581</v>
+        <v>0.00024309330720239427</v>
       </c>
       <c r="DI3">
-        <v>0.064293665400410455</v>
+        <v>0.064512483885875271</v>
       </c>
       <c r="DJ3">
-        <v>0.038605608598649858</v>
+        <v>0.044184682372439874</v>
       </c>
       <c r="DK3">
-        <v>0.014520544443796898</v>
+        <v>0.014532459854752157</v>
       </c>
       <c r="DL3">
-        <v>0.008779036413044318</v>
+        <v>0.0088075241253688739</v>
       </c>
       <c r="DM3">
-        <v>0.018566267887762153</v>
+        <v>0.018560695461353392</v>
       </c>
       <c r="DN3">
-        <v>0.012092042796146726</v>
+        <v>0.012003675965916965</v>
       </c>
       <c r="DO3">
         <v>0.00784114052953157</v>
       </c>
       <c r="DP3">
-        <v>0.002488936956729883</v>
+        <v>0.0024824149063731754</v>
       </c>
       <c r="DQ3">
-        <v>0.087266379932168348</v>
+        <v>0.087477870593911461</v>
       </c>
       <c r="DR3">
-        <v>0.018422520084294781</v>
+        <v>0.020083158272514657</v>
       </c>
       <c r="DS3">
-        <v>0.028111622054748264</v>
+        <v>0.028220037185182918</v>
       </c>
       <c r="DT3">
-        <v>0.024812830230538565</v>
+        <v>0.024758610323869702</v>
       </c>
       <c r="DU3">
-        <v>0.008347197090891087</v>
+        <v>0.0083086584354571461</v>
       </c>
     </row>
   </sheetData>
